--- a/data/product_parameters.xlsx
+++ b/data/product_parameters.xlsx
@@ -52,30 +52,6 @@
   </si>
   <si>
     <t>order</t>
-  </si>
-  <si>
-    <t>short-nike-kids</t>
-  </si>
-  <si>
-    <t>Transpirante</t>
-  </si>
-  <si>
-    <t>Nike</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>Material</t>
-  </si>
-  <si>
-    <t>Textil y sintetico</t>
-  </si>
-  <si>
-    <t>Uso recomendado</t>
-  </si>
-  <si>
-    <t>Lifestyle y entrenamiento</t>
   </si>
 </sst>
 </file>
@@ -451,50 +427,14 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
+      <c r="A2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError sqref="A1:D1 A4:D4 B3:D3 B2:D2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>